--- a/docentes/González Nuñez Veronica - Estadisticos 20221.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -82,34 +82,16 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>CHACÓN</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>PAZ</t>
@@ -118,19 +100,10 @@
     <t>ESTRADA</t>
   </si>
   <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
     <t>SAID ANDRES</t>
   </si>
   <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>KATHIA</t>
+    <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>JAIME</t>
@@ -534,22 +507,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>4</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>29</v>
       </c>
       <c r="G2">
-        <v>87.88</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -703,13 +676,13 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -857,22 +830,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>4</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>29</v>
       </c>
       <c r="G2">
-        <v>87.88</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -986,7 +959,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1018,16 +991,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920051</v>
+        <v>20330051920082</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
         <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1041,139 +1014,70 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920082</v>
+        <v>21330051920195</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920091</v>
+        <v>21330051920096</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920026</v>
+        <v>21330051920041</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920072</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920096</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920041</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20221.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -97,9 +97,6 @@
     <t>PAZ</t>
   </si>
   <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
     <t>SAID ANDRES</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
   </si>
   <si>
     <t>JAIME</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
   </si>
 </sst>
 </file>
@@ -679,16 +673,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H2">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -702,16 +699,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>73.68000000000001</v>
+      </c>
+      <c r="H3">
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -725,16 +725,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>81.25</v>
+      </c>
+      <c r="H4">
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -748,16 +751,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H5">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -771,16 +777,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>72.73</v>
+      </c>
+      <c r="H6">
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -845,7 +854,7 @@
         <v>85.29000000000001</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -888,16 +897,16 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -949,7 +958,7 @@
         <v>81.81999999999999</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -959,7 +968,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1000,7 +1009,7 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1023,7 +1032,7 @@
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1046,7 +1055,7 @@
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1055,29 +1064,6 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920041</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20221.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20221.xlsx
@@ -88,19 +88,19 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
     <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>JAIME</t>
@@ -1000,7 +1000,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920082</v>
+        <v>21330051920195</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1012,10 +1012,10 @@
         <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1023,7 +1023,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920195</v>
+        <v>20330051920082</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -1035,13 +1035,13 @@
         <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">

--- a/docentes/González Nuñez Veronica - Estadisticos 20221.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -85,25 +85,31 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>LUIS ENRIQUE</t>
   </si>
   <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
     <t>SAID ANDRES</t>
   </si>
   <si>
-    <t>JAIME</t>
+    <t>ALMA KAREN</t>
   </si>
 </sst>
 </file>
@@ -504,19 +510,19 @@
         <v>34</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>4</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -530,19 +536,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -556,10 +562,10 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>29</v>
@@ -568,7 +574,7 @@
         <v>90.63</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -582,19 +588,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>65.38</v>
+        <v>76.92</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -608,19 +614,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>81.81999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -673,19 +679,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -699,19 +705,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>73.68000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -725,19 +731,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>81.25</v>
+        <v>93.75</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -751,19 +757,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>65.38</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -777,19 +783,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>72.73</v>
+        <v>87.88</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -842,19 +848,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>85.29000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -868,19 +874,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>89.47</v>
+        <v>86.84</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -894,10 +900,10 @@
         <v>32</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>2</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>30</v>
@@ -906,7 +912,7 @@
         <v>93.75</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -920,10 +926,10 @@
         <v>26</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>9</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>17</v>
@@ -932,7 +938,7 @@
         <v>65.38</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -946,19 +952,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>81.81999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="H6">
-        <v>9.300000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -968,7 +974,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1006,10 +1012,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1023,22 +1029,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920082</v>
+        <v>21330051920109</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1046,24 +1052,47 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920096</v>
+        <v>20330051920082</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920103</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
         <v>11</v>
       </c>
-      <c r="G4">
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20221.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,9 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>SANJUAN</t>
   </si>
   <si>
@@ -97,6 +100,9 @@
     <t>VERA</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>OFICIAL</t>
   </si>
   <si>
@@ -104,6 +110,9 @@
   </si>
   <si>
     <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
   </si>
   <si>
     <t>SAID ANDRES</t>
@@ -974,7 +983,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1012,10 +1021,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1035,10 +1044,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1052,16 +1061,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920082</v>
+        <v>19330051920051</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1075,24 +1084,47 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
+        <v>20330051920082</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
         <v>21330051920103</v>
       </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
         <v>24</v>
       </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
         <v>11</v>
       </c>
-      <c r="G5">
+      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20221.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -82,31 +82,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>SANJUAN</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
@@ -869,7 +866,7 @@
         <v>82.34999999999999</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -921,7 +918,7 @@
         <v>93.75</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -983,7 +980,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1015,7 +1012,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920195</v>
+        <v>21330051920109</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1030,7 +1027,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1038,7 +1035,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920109</v>
+        <v>19330051920051</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1050,10 +1047,10 @@
         <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1061,7 +1058,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920051</v>
+        <v>20330051920082</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1084,10 +1081,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920082</v>
+        <v>21330051920103</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
         <v>28</v>
@@ -1096,35 +1093,12 @@
         <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920103</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20221.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,42 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
   </si>
 </sst>
 </file>
@@ -857,16 +821,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>82.34999999999999</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -883,13 +847,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>86.84</v>
+        <v>97.37</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -935,16 +899,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>65.38</v>
+        <v>92.31</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -961,16 +925,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>87.88</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -980,7 +944,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1010,98 +974,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920109</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920051</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920082</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920103</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
